--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261020.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261020.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>35,492,000</t>
+          <t>7,188,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>7,188,000</t>
+          <t>35,492,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
